--- a/artfynd/A 26855-2022 artfynd.xlsx
+++ b/artfynd/A 26855-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 26855-2022 artfynd.xlsx
+++ b/artfynd/A 26855-2022 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>63628770</v>
       </c>
       <c r="B2" t="n">
-        <v>95522</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97463</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>384260.5758991487</v>
+        <v>384261</v>
       </c>
       <c r="R2" t="n">
-        <v>6208803.504036731</v>
+        <v>6208804</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -748,19 +743,9 @@
           <t>2004-06-16</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2004-06-16</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -809,12 +794,7 @@
         <v>63628776</v>
       </c>
       <c r="B3" t="n">
-        <v>101854</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104211</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -846,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>384260.5758991487</v>
+        <v>384261</v>
       </c>
       <c r="R3" t="n">
-        <v>6208803.504036731</v>
+        <v>6208804</v>
       </c>
       <c r="S3" t="n">
         <v>100</v>
@@ -879,19 +859,9 @@
           <t>2004-06-16</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2004-06-16</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">

--- a/artfynd/A 26855-2022 artfynd.xlsx
+++ b/artfynd/A 26855-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63628770</v>
       </c>
       <c r="B2" t="n">
-        <v>97463</v>
+        <v>97465</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>63628776</v>
       </c>
       <c r="B3" t="n">
-        <v>104211</v>
+        <v>104223</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 26855-2022 artfynd.xlsx
+++ b/artfynd/A 26855-2022 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>63628776</v>
       </c>
       <c r="B3" t="n">
-        <v>104223</v>
+        <v>104232</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 26855-2022 artfynd.xlsx
+++ b/artfynd/A 26855-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63628770</v>
       </c>
       <c r="B2" t="n">
-        <v>97465</v>
+        <v>97466</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>63628776</v>
       </c>
       <c r="B3" t="n">
-        <v>104232</v>
+        <v>104235</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 26855-2022 artfynd.xlsx
+++ b/artfynd/A 26855-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63628770</v>
       </c>
       <c r="B2" t="n">
-        <v>97466</v>
+        <v>97493</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>63628776</v>
       </c>
       <c r="B3" t="n">
-        <v>104235</v>
+        <v>104262</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 26855-2022 artfynd.xlsx
+++ b/artfynd/A 26855-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63628770</v>
       </c>
       <c r="B2" t="n">
-        <v>97493</v>
+        <v>97499</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>63628776</v>
       </c>
       <c r="B3" t="n">
-        <v>104262</v>
+        <v>104268</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 26855-2022 artfynd.xlsx
+++ b/artfynd/A 26855-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63628770</v>
       </c>
       <c r="B2" t="n">
-        <v>97499</v>
+        <v>97506</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>63628776</v>
       </c>
       <c r="B3" t="n">
-        <v>104268</v>
+        <v>104275</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 26855-2022 artfynd.xlsx
+++ b/artfynd/A 26855-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63628770</v>
       </c>
       <c r="B2" t="n">
-        <v>97506</v>
+        <v>97510</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>63628776</v>
       </c>
       <c r="B3" t="n">
-        <v>104275</v>
+        <v>104279</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 26855-2022 artfynd.xlsx
+++ b/artfynd/A 26855-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63628770</v>
       </c>
       <c r="B2" t="n">
-        <v>97510</v>
+        <v>97517</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>63628776</v>
       </c>
       <c r="B3" t="n">
-        <v>104279</v>
+        <v>104286</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 26855-2022 artfynd.xlsx
+++ b/artfynd/A 26855-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63628770</v>
       </c>
       <c r="B2" t="n">
-        <v>97520</v>
+        <v>97525</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>63628776</v>
       </c>
       <c r="B3" t="n">
-        <v>104289</v>
+        <v>104294</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 26855-2022 artfynd.xlsx
+++ b/artfynd/A 26855-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63628770</v>
       </c>
       <c r="B2" t="n">
-        <v>97525</v>
+        <v>97533</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>63628776</v>
       </c>
       <c r="B3" t="n">
-        <v>104294</v>
+        <v>104302</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 26855-2022 artfynd.xlsx
+++ b/artfynd/A 26855-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63628770</v>
       </c>
       <c r="B2" t="n">
-        <v>97533</v>
+        <v>97543</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>63628776</v>
       </c>
       <c r="B3" t="n">
-        <v>104302</v>
+        <v>104312</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
